--- a/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_301_CALIFICADO.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_301_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1368,7 +1352,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1571,7 +1551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1762,11 +1742,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1774,7 +1750,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1965,11 +1941,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1977,7 +1949,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2168,11 +2140,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2180,7 +2148,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2371,11 +2339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2383,7 +2347,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2574,11 +2538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2586,7 +2546,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2777,11 +2737,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2789,7 +2745,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2980,11 +2936,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2992,7 +2944,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3183,11 +3135,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3195,7 +3143,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3386,11 +3334,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3398,7 +3342,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3589,11 +3533,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3601,7 +3541,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3792,11 +3732,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3804,7 +3740,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3995,11 +3931,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4007,7 +3939,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4198,11 +4130,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4210,7 +4138,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4401,11 +4329,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4413,7 +4337,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4600,11 +4524,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4612,7 +4532,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4803,11 +4723,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4815,7 +4731,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5006,11 +4922,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5018,7 +4930,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5209,11 +5121,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5221,7 +5129,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5412,11 +5320,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5424,7 +5328,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5615,11 +5519,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5627,7 +5527,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5818,11 +5718,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5830,7 +5726,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6017,11 +5913,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6029,7 +5921,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6220,11 +6112,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6232,7 +6120,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6423,11 +6311,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6435,7 +6319,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6626,11 +6510,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6638,7 +6518,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6829,11 +6709,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6841,7 +6717,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7032,11 +6908,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7044,7 +6916,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7235,11 +7107,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7247,7 +7115,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7438,11 +7306,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7450,7 +7314,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7637,11 +7501,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7649,7 +7509,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7840,11 +7700,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7852,7 +7708,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8043,11 +7899,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8055,7 +7907,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8246,11 +8098,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8258,7 +8106,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8449,11 +8297,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8461,7 +8305,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8652,11 +8496,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8664,7 +8504,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8855,11 +8695,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8867,7 +8703,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9058,11 +8894,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9070,7 +8902,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9261,11 +9093,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9273,7 +9101,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9464,11 +9292,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9476,7 +9300,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9667,11 +9491,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9679,7 +9499,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9870,11 +9690,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9882,7 +9698,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10073,11 +9889,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10085,7 +9897,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10276,11 +10088,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10288,7 +10096,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10475,11 +10283,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10487,7 +10291,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10678,11 +10482,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10690,7 +10490,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10877,11 +10677,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10889,7 +10685,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11080,11 +10876,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11092,7 +10884,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11283,11 +11075,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11295,7 +11083,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11486,11 +11274,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11498,7 +11282,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11685,11 +11469,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11697,7 +11477,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11888,11 +11668,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11900,7 +11676,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12091,11 +11867,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12103,7 +11875,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12294,11 +12066,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12306,7 +12074,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12493,11 +12261,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12505,7 +12269,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12696,11 +12460,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12708,7 +12468,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12899,11 +12659,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12911,7 +12667,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13102,11 +12858,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13114,7 +12866,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13301,11 +13053,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13313,7 +13061,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13504,11 +13252,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13516,7 +13260,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13707,11 +13451,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13719,7 +13459,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13910,11 +13650,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13922,7 +13658,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14113,11 +13849,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14125,7 +13857,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14316,11 +14048,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14328,7 +14056,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14519,11 +14247,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14531,7 +14255,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14722,11 +14446,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14734,7 +14454,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14921,11 +14641,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14933,7 +14649,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15120,11 +14836,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15132,7 +14844,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15319,11 +15031,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15331,7 +15039,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15522,11 +15230,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15534,7 +15238,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15725,11 +15429,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15737,7 +15437,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15924,11 +15624,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15936,7 +15632,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -16127,11 +15823,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16139,7 +15831,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -16326,11 +16018,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16338,7 +16026,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -16529,11 +16217,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16541,7 +16225,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -16732,11 +16416,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16744,7 +16424,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -16935,11 +16615,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16947,7 +16623,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -17138,11 +16814,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17150,7 +16822,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -17341,11 +17013,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17353,7 +17021,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -17544,11 +17212,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17556,7 +17220,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
